--- a/data/trans_dic/P33_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 21,4</t>
+          <t>14,05; 21,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,67; 28,19</t>
+          <t>19,4; 28,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 25,98</t>
+          <t>17,73; 25,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,56; 27,62</t>
+          <t>19,29; 26,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 23,06</t>
+          <t>14,27; 22,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,02; 24,86</t>
+          <t>15,94; 24,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 25,14</t>
+          <t>15,87; 24,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,26; 31,47</t>
+          <t>23,56; 30,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 21,01</t>
+          <t>15,48; 20,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 25,81</t>
+          <t>19,22; 25,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 23,7</t>
+          <t>17,93; 23,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 27,88</t>
+          <t>22,51; 28,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,99</t>
+          <t>9,8; 18,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 30,47</t>
+          <t>20,97; 29,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,43; 30,8</t>
+          <t>21,29; 30,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 27,89</t>
+          <t>18,94; 26,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 22,39</t>
+          <t>14,16; 21,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,19; 33,14</t>
+          <t>23,39; 33,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 24,84</t>
+          <t>16,11; 25,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,16; 32,2</t>
+          <t>23,69; 31,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,63</t>
+          <t>13,24; 18,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,23; 30,32</t>
+          <t>22,96; 30,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,32; 26,52</t>
+          <t>20,13; 26,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,45; 27,79</t>
+          <t>21,98; 27,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 22,77</t>
+          <t>16,29; 23,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 30,93</t>
+          <t>23,3; 30,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 29,01</t>
+          <t>21,45; 29,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 34,16</t>
+          <t>28,23; 37,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 33,26</t>
+          <t>19,83; 33,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,68; 35,35</t>
+          <t>23,82; 35,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 32,66</t>
+          <t>17,81; 31,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,59; 35,59</t>
+          <t>23,21; 34,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,22</t>
+          <t>17,59; 23,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,86; 31,05</t>
+          <t>24,67; 30,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,44; 28,48</t>
+          <t>21,37; 28,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 32,62</t>
+          <t>27,81; 34,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,73; 24,4</t>
+          <t>19,85; 24,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 29,97</t>
+          <t>24,56; 30,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,93; 27,4</t>
+          <t>22,08; 27,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,04; 30,16</t>
+          <t>23,18; 28,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 24,43</t>
+          <t>18,72; 24,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 32,51</t>
+          <t>25,68; 32,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 32,42</t>
+          <t>25,88; 32,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,95; 74,48</t>
+          <t>31,41; 36,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,91; 23,59</t>
+          <t>19,75; 23,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 30,28</t>
+          <t>25,95; 30,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,28; 28,34</t>
+          <t>24,18; 28,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 57,51</t>
+          <t>27,36; 31,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 25,33</t>
+          <t>16,99; 25,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,64; 32,49</t>
+          <t>24,44; 32,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,96</t>
+          <t>19,16; 25,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,82; 30,07</t>
+          <t>21,49; 29,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,85; 28,41</t>
+          <t>21,03; 28,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 41,51</t>
+          <t>34,26; 41,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,91; 34,78</t>
+          <t>27,58; 34,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,58; 35,08</t>
+          <t>31,5; 37,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,55; 26,41</t>
+          <t>20,65; 26,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 37,05</t>
+          <t>31,25; 36,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,89; 29,54</t>
+          <t>24,69; 29,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,96; 32,14</t>
+          <t>28,49; 32,96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,26</t>
+          <t>4,81; 11,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,82; 22,36</t>
+          <t>12,86; 21,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,57; 20,15</t>
+          <t>11,56; 20,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 19,11</t>
+          <t>5,09; 17,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,58; 30,83</t>
+          <t>25,68; 30,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,16; 39,87</t>
+          <t>34,15; 39,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,52; 35,44</t>
+          <t>29,47; 35,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,13; 30,75</t>
+          <t>25,02; 30,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,17; 26,39</t>
+          <t>22,04; 26,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,59; 35,75</t>
+          <t>30,56; 35,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,4; 31,51</t>
+          <t>26,33; 31,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,86; 26,19</t>
+          <t>21,32; 26,68</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,9</t>
+          <t>17,29; 19,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,35; 27,5</t>
+          <t>24,39; 27,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,69; 24,76</t>
+          <t>21,64; 24,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,67; 25,56</t>
+          <t>22,93; 26,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,64; 25,6</t>
+          <t>22,66; 25,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,84; 34,21</t>
+          <t>30,89; 34,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,84; 30,11</t>
+          <t>27,03; 30,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,25; 48,48</t>
+          <t>29,31; 32,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,32; 22,35</t>
+          <t>20,4; 22,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,17; 30,4</t>
+          <t>28,16; 30,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,72; 26,94</t>
+          <t>24,75; 26,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,55; 35,75</t>
+          <t>26,73; 28,78</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114946</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121646</t>
+          <t>131260</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>236591</t>
+          <t>254612</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66866; 99893</t>
+          <t>65559; 101749</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86013; 123235</t>
+          <t>84827; 123673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75204; 111493</t>
+          <t>76076; 110871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96836; 136760</t>
+          <t>104172; 144964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42938; 70707</t>
+          <t>43769; 70431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47243; 78166</t>
+          <t>50139; 78471</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55246; 87263</t>
+          <t>55081; 85948</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107251; 139101</t>
+          <t>113671; 147541</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118344; 162516</t>
+          <t>119759; 161270</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146254; 194034</t>
+          <t>144437; 191592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137926; 183950</t>
+          <t>139143; 185776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>213989; 261348</t>
+          <t>230187; 287227</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102886</t>
+          <t>107384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>104348</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>207233</t>
+          <t>221894</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37545; 65496</t>
+          <t>35669; 65668</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88395; 127337</t>
+          <t>87608; 124654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80654; 115895</t>
+          <t>80118; 116324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87274; 124643</t>
+          <t>90298; 126787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52516; 83066</t>
+          <t>52524; 80822</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78380; 112007</t>
+          <t>79066; 113936</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60261; 92468</t>
+          <t>59968; 93879</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90767; 120984</t>
+          <t>98334; 130952</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96097; 136914</t>
+          <t>97292; 138591</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175614; 229147</t>
+          <t>173543; 227175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152082; 198556</t>
+          <t>150677; 199780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184687; 228625</t>
+          <t>196034; 244716</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135899</t>
+          <t>149685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48503</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>184402</t>
+          <t>202550</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84830; 122234</t>
+          <t>87425; 123954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145621; 194067</t>
+          <t>146183; 193256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110551; 150929</t>
+          <t>111586; 151760</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52435; 225446</t>
+          <t>130417; 171225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31763; 54730</t>
+          <t>32626; 55346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60807; 90771</t>
+          <t>61171; 92349</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28062; 52902</t>
+          <t>28854; 51337</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39883; 57710</t>
+          <t>42383; 62607</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125325; 169898</t>
+          <t>123393; 167436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219776; 274551</t>
+          <t>218097; 273253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146299; 194347</t>
+          <t>145825; 191548</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78963; 268196</t>
+          <t>179265; 225467</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262609</t>
+          <t>276354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>460412</t>
+          <t>285303</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>723022</t>
+          <t>561658</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>240071; 296847</t>
+          <t>241496; 301655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>284379; 345201</t>
+          <t>282951; 346877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>251420; 314169</t>
+          <t>253146; 312215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>235919; 295956</t>
+          <t>250152; 309949</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130911; 172769</t>
+          <t>132365; 175921</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198025; 249225</t>
+          <t>196904; 249604</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>211412; 266821</t>
+          <t>213064; 266135</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>314900; 711873</t>
+          <t>262813; 309346</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>383027; 453709</t>
+          <t>380009; 455209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>500086; 580927</t>
+          <t>497945; 579024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>478280; 558133</t>
+          <t>476244; 555953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>562678; 1114068</t>
+          <t>524200; 601106</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117952</t>
+          <t>139602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>247535</t>
+          <t>272405</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>365488</t>
+          <t>412008</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58488; 87512</t>
+          <t>58703; 89405</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>125497; 165443</t>
+          <t>124468; 164112</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118726; 160853</t>
+          <t>118732; 159392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99122; 136613</t>
+          <t>117677; 161878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118570; 161597</t>
+          <t>119617; 162701</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>260371; 315729</t>
+          <t>260568; 314360</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>205422; 255994</t>
+          <t>203016; 251788</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>182599; 283677</t>
+          <t>251342; 295688</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>187844; 241452</t>
+          <t>188802; 241156</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>399693; 470413</t>
+          <t>396805; 464625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337430; 400460</t>
+          <t>334688; 400604</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>302621; 405895</t>
+          <t>383360; 443569</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>202818</t>
+          <t>226226</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>226001</t>
+          <t>249805</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14331; 33063</t>
+          <t>14139; 33290</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34082; 59454</t>
+          <t>34189; 58411</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33231; 57859</t>
+          <t>33187; 58003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11370; 45159</t>
+          <t>11903; 41864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>316637; 381719</t>
+          <t>317947; 381694</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>377211; 440321</t>
+          <t>377099; 439844</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>317813; 381582</t>
+          <t>317306; 381148</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>184008; 225179</t>
+          <t>203527; 250345</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>339630; 404140</t>
+          <t>337581; 408308</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>419096; 489887</t>
+          <t>418780; 488879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>360021; 429707</t>
+          <t>359025; 428959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>202037; 253696</t>
+          <t>223244; 279401</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>757474</t>
+          <t>819956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1185262</t>
+          <t>1082570</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1942737</t>
+          <t>1902527</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>555711; 641365</t>
+          <t>557254; 641776</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>830123; 937733</t>
+          <t>831718; 938907</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>732789; 836501</t>
+          <t>731237; 830283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>513137; 836656</t>
+          <t>765662; 871756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>759777; 859289</t>
+          <t>760326; 857436</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1091889; 1211162</t>
+          <t>1093626; 1206579</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>944136; 1059074</t>
+          <t>950581; 1057727</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1016867; 1685400</t>
+          <t>1034053; 1130749</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1336893; 1470379</t>
+          <t>1342274; 1477478</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1957698; 2112769</t>
+          <t>1957235; 2115135</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1704963; 1858037</t>
+          <t>1706973; 1852675</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1724707; 2413375</t>
+          <t>1835925; 1976693</t>
         </is>
       </c>
     </row>
